--- a/artfynd/A 30687-2025 artfynd.xlsx
+++ b/artfynd/A 30687-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5280745</v>
+        <v>141791</v>
       </c>
       <c r="B2" t="n">
-        <v>98430</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Karlberg, 400 m NO om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>707382.5073877329</v>
+        <v>707409</v>
       </c>
       <c r="R2" t="n">
-        <v>6643710.793889105</v>
+        <v>6643651</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +747,9 @@
           <t>2009-09-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-09-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6688131</v>
+        <v>298827</v>
       </c>
       <c r="B3" t="n">
-        <v>86194</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>239233</v>
+        <v>1054</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ekvaxskivling</t>
+          <t>Stinkbrosking</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrophorus cossus</t>
+          <t>Gymnopus foetidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sowerby) Fr.</t>
+          <t>(Sowerby) P.M.Kirk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +816,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707382.5073877329</v>
+        <v>707409</v>
       </c>
       <c r="R3" t="n">
-        <v>6643710.793889105</v>
+        <v>6643651</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,19 +849,14 @@
           <t>2009-09-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-09-22</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>massvis på döda hasselgrenar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,12 +891,7 @@
         <v>5050727</v>
       </c>
       <c r="B4" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707299.4696590086</v>
+        <v>707299</v>
       </c>
       <c r="R4" t="n">
-        <v>6643726.769562791</v>
+        <v>6643727</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,19 +956,9 @@
           <t>2009-09-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2009-09-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,57 +990,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>141791</v>
+        <v>5280745</v>
       </c>
       <c r="B5" t="n">
-        <v>90137</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>366</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Karlberg, 400 m NO om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707408.5140274488</v>
+        <v>707383</v>
       </c>
       <c r="R5" t="n">
-        <v>6643651.376244379</v>
+        <v>6643711</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,19 +1058,9 @@
           <t>2009-09-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2009-09-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,128 +1089,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>298827</v>
-      </c>
-      <c r="B6" t="n">
-        <v>87252</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1054</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Stinkbrosking</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Gymnopus foetidus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Sowerby:Fr.) P.M.Kirk</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Karlberg, 400 m NO om, Upl</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>707408.5140274488</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6643651.376244379</v>
-      </c>
-      <c r="S6" t="n">
-        <v>25</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Söderby-Karl</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2009-09-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2009-09-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>massvis på döda hasselgrenar</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>ädellövskog</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30687-2025 artfynd.xlsx
+++ b/artfynd/A 30687-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/141791</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/298827</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5050727</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,8 +1109,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5280745</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>